--- a/presentations/heatmap_byhand/xlsx/baseline_methods/chatgpt/risk_ranking_slackMCP_chatgpt_security.xlsx
+++ b/presentations/heatmap_byhand/xlsx/baseline_methods/chatgpt/risk_ranking_slackMCP_chatgpt_security.xlsx
@@ -80,7 +80,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -120,6 +120,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED7D31"/>
+        <bgColor rgb="FFED7D31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
+        <bgColor rgb="FFFFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+        <bgColor rgb="FF70AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -223,7 +247,7 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -285,6 +309,75 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -653,12 +746,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1">
@@ -677,6 +771,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -687,9 +786,14 @@
           <t>slack_get_channel_history</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Access to channel history can reveal sensitive discussions.</t>
         </is>
       </c>
     </row>
@@ -702,9 +806,14 @@
           <t>slack_get_thread_replies</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Thread replies can contain sensitive follow-up information.</t>
         </is>
       </c>
     </row>
@@ -717,9 +826,14 @@
           <t>slack_get_user_profile</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>User profiles can contain personal information.</t>
         </is>
       </c>
     </row>
@@ -732,9 +846,14 @@
           <t>slack_post_message</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Posting messages can disrupt communication channels.</t>
         </is>
       </c>
     </row>
@@ -747,9 +866,14 @@
           <t>slack_reply_to_thread</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Replying to threads can spread misinformation.</t>
         </is>
       </c>
     </row>
@@ -762,9 +886,14 @@
           <t>slack_get_users</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Access to user lists can reveal organizational structure.</t>
         </is>
       </c>
     </row>
@@ -777,9 +906,14 @@
           <t>slack_list_channels</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Low</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Listing channels generally poses low risk.</t>
         </is>
       </c>
     </row>
@@ -792,9 +926,14 @@
           <t>slack_add_reaction</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Low</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Adding reactions is generally harmless.</t>
         </is>
       </c>
     </row>
@@ -809,12 +948,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1">
@@ -833,6 +973,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -843,9 +988,14 @@
           <t>Management</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="C2" s="27" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Contains strategic and sensitive management discussions.</t>
         </is>
       </c>
     </row>
@@ -858,9 +1008,14 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Contains sensitive employee information and discussions.</t>
         </is>
       </c>
     </row>
@@ -873,9 +1028,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Low</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Contains information intended for public access.</t>
         </is>
       </c>
     </row>
@@ -888,9 +1048,14 @@
           <t>Supervisor</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Contains supervisory communications that may be sensitive.</t>
         </is>
       </c>
     </row>
@@ -903,9 +1068,14 @@
           <t>Researcher</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Contains research discussions that may be proprietary.</t>
         </is>
       </c>
     </row>
@@ -918,11 +1088,12 @@
           <t>Techinical</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -935,12 +1106,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1">
@@ -959,6 +1131,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -969,9 +1146,14 @@
           <t>User PII (emails, phones, titles)</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Exposure of PII can lead to identity theft.</t>
         </is>
       </c>
     </row>
@@ -984,9 +1166,14 @@
           <t>Private Channel Messages</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Contains confidential communications.</t>
         </is>
       </c>
     </row>
@@ -999,9 +1186,14 @@
           <t>Public Channel Messages</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Generally intended for wider audience, less sensitive.</t>
         </is>
       </c>
     </row>
@@ -1014,9 +1206,14 @@
           <t>Team Metadata</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Contains organizational information that could be sensitive.</t>
         </is>
       </c>
     </row>
@@ -1111,42 +1308,42 @@
           <t>User PII (emails, phones, titles)</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F2" s="17" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I2" s="18" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="D2" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E2" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F2" s="30" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G2" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H2" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J2" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K2" s="29" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1160,42 +1357,42 @@
           <t>Private Channel Messages</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G3" s="17" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I3" s="18" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F3" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G3" s="30" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H3" s="30" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I3" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J3" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1209,42 +1406,42 @@
           <t>Public Channel Messages</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H4" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I4" s="18" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F4" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G4" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H4" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J4" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K4" s="29" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1258,42 +1455,42 @@
           <t>Team Metadata</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H5" s="30" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J5" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K5" s="29" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1313,42 +1510,42 @@
           <t>User PII (emails, phones, titles)</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H6" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J6" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1362,42 +1559,42 @@
           <t>Private Channel Messages</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F7" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G7" s="30" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H7" s="30" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J7" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K7" s="29" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1411,42 +1608,42 @@
           <t>Public Channel Messages</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G8" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H8" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J8" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K8" s="29" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1460,42 +1657,42 @@
           <t xml:space="preserve"> Team Metadata</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G9" s="30" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H9" s="30" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I9" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J9" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1515,42 +1712,42 @@
           <t>Public Channel Messages</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E10" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H10" s="36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I10" s="37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J10" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K10" s="38" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1563,42 +1760,42 @@
           <t>Workspace / Team Metadata</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E11" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F11" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H11" s="36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I11" s="37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J11" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K11" s="38" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1618,42 +1815,42 @@
           <t>User PII (emails, phones, titles)</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E12" s="39" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F12" s="39" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G12" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H12" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I12" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J12" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1666,42 +1863,42 @@
           <t>Private Channel Messages</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="D13" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E13" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H13" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I13" s="42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J13" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K13" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1714,42 +1911,42 @@
           <t>Public Channel Messages</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H14" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I14" s="42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J14" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K14" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1762,42 +1959,42 @@
           <t>Workspace / Team Metadata</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="D15" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F15" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G15" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H15" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I15" s="42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J15" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K15" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1817,42 +2014,42 @@
           <t>User PII (emails, phones, titles)</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G16" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H16" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I16" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J16" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K16" s="29" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1865,42 +2062,42 @@
           <t>Private Channel Messages</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="D17" s="44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E17" s="44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F17" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G17" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I17" s="42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J17" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K17" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1913,42 +2110,42 @@
           <t>Public Channel Messages</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E18" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F18" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H18" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I18" s="42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J18" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K18" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1961,42 +2158,42 @@
           <t>Workspace / Team Metadata</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="D19" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E19" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F19" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G19" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H19" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I19" s="42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J19" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K19" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2016,42 +2213,42 @@
           <t>User PII (emails, phones, titles)</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G20" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H20" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I20" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J20" s="32" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K20" s="29" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2064,42 +2261,42 @@
           <t>Private Channel Messages</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="D21" s="44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E21" s="44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G21" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H21" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I21" s="42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J21" s="41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K21" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2112,42 +2309,42 @@
           <t>Public Channel Messages</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E22" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G22" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H22" s="45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I22" s="37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J22" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K22" s="38" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2160,42 +2357,42 @@
           <t>Workspace / Team Metadata</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G23" s="36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H23" s="36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I23" s="37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J23" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K23" s="38" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
